--- a/Cardiologie/Excel/cardio_4.xlsx
+++ b/Cardiologie/Excel/cardio_4.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\moito\Desktop\Sérieux\Projet\Site web\Cardiologie\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{550AC74F-8D35-4FAA-9DFA-0764F1718DA6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{676A5CCA-9060-46EB-B900-8DBCBF91559D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2070" yWindow="3930" windowWidth="25830" windowHeight="11385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1725" yWindow="3585" windowWidth="21600" windowHeight="11385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -6140,7 +6140,7 @@
         <v>98</v>
       </c>
       <c r="C100" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D100" s="3" t="s">
         <v>679</v>
